--- a/owlcms/src/main/resources/templates/protocol/SnCJTot-LETTER.xlsx
+++ b/owlcms/src/main/resources/templates/protocol/SnCJTot-LETTER.xlsx
@@ -1943,379 +1943,379 @@
       <left/>
       <right/>
       <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left/>
@@ -2323,8 +2323,8 @@
       <top style="thin">
         <color indexed="8"/>
       </top>
-      <diagonal/>
-      <bottom/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left/>
@@ -2332,8 +2332,8 @@
       <top style="thin">
         <color indexed="8"/>
       </top>
-      <diagonal/>
-      <bottom/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left/>
@@ -2341,50 +2341,50 @@
       <top style="thin">
         <color indexed="8"/>
       </top>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left/>
@@ -2392,8 +2392,8 @@
       <top style="thin">
         <color indexed="64"/>
       </top>
-      <diagonal/>
-      <bottom/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left/>
@@ -2401,8 +2401,8 @@
       <top style="thin">
         <color indexed="64"/>
       </top>
-      <diagonal/>
-      <bottom/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left/>
@@ -2410,8 +2410,8 @@
       <top style="thin">
         <color indexed="64"/>
       </top>
-      <diagonal/>
-      <bottom/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left/>
@@ -2419,8 +2419,8 @@
       <top style="thin">
         <color indexed="64"/>
       </top>
-      <diagonal/>
-      <bottom/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left/>
@@ -2428,8 +2428,8 @@
       <top style="thin">
         <color indexed="64"/>
       </top>
-      <diagonal/>
-      <bottom/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left/>
@@ -2437,8 +2437,8 @@
       <top style="thin">
         <color indexed="64"/>
       </top>
-      <diagonal/>
-      <bottom/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left/>
@@ -2446,8 +2446,8 @@
       <top style="thin">
         <color indexed="64"/>
       </top>
-      <diagonal/>
-      <bottom/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left/>
@@ -2455,8 +2455,8 @@
       <top style="thin">
         <color indexed="64"/>
       </top>
-      <diagonal/>
-      <bottom/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left/>
@@ -2464,134 +2464,134 @@
       <top style="thin">
         <color indexed="64"/>
       </top>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="19">
@@ -3047,16 +3047,16 @@
       <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
     </xf>
     <xf numFmtId="49" fontId="71" fillId="0" borderId="66" xfId="0" applyNumberFormat="1" applyBorder="1" applyProtection="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="0"/>
       <protection locked="0"/>
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="0"/>
     </xf>
     <xf numFmtId="49" fontId="72" fillId="0" borderId="67" xfId="0" applyNumberFormat="1" applyBorder="1" applyProtection="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" shrinkToFit="0"/>
       <protection locked="0"/>
-      <alignment horizontal="right" vertical="center" wrapText="1" shrinkToFit="0"/>
     </xf>
     <xf numFmtId="49" fontId="73" fillId="0" borderId="68" xfId="0" applyNumberFormat="1" applyBorder="1" applyProtection="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
       <protection locked="0"/>
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
     </xf>
     <xf numFmtId="0" fontId="74" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="0"/>
@@ -3224,16 +3224,16 @@
       <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
     </xf>
     <xf numFmtId="0" fontId="128" fillId="0" borderId="123" xfId="0" applyProtection="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="0"/>
       <protection locked="0"/>
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="0"/>
     </xf>
     <xf numFmtId="0" fontId="129" fillId="0" borderId="124" xfId="0" applyProtection="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" shrinkToFit="0"/>
       <protection locked="0"/>
-      <alignment horizontal="right" vertical="center" wrapText="1" shrinkToFit="0"/>
     </xf>
     <xf numFmtId="0" fontId="130" fillId="0" borderId="125" xfId="0" applyProtection="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
       <protection locked="0"/>
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
     </xf>
     <xf numFmtId="0" fontId="131" fillId="0" borderId="126" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="0"/>
@@ -4679,16 +4679,6 @@
     <mergeCell ref="A4:C4"/>
     <mergeCell ref="D4:V4"/>
   </mergeCells>
-  <conditionalFormatting sqref="D8">
-    <cfRule type="expression" dxfId="1" priority="8" stopIfTrue="1">
-      <formula>AND((#REF!),#REF!,#REF!)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D11:F13">
-    <cfRule type="expression" dxfId="0" priority="3" stopIfTrue="1">
-      <formula>AND((#REF!),#REF!,#REF!)</formula>
-    </cfRule>
-  </conditionalFormatting>
   <dataValidations count="3">
     <dataValidation showErrorMessage="1" sqref="H4 F23 C20 C17 S17 L17 F17 F20 C23 L20 S20 S23" ns1:uid="{00000000-0002-0000-0000-000000000000}"/>
     <dataValidation type="decimal" allowBlank="1" showErrorMessage="1" sqref="F10 H11:H13" ns1:uid="{00000000-0002-0000-0000-000001000000}">
@@ -4700,7 +4690,6 @@
       <formula2>200</formula2>
     </dataValidation>
   </dataValidations>
-  <hyperlinks/>
   <pageMargins left="0.31496062992125984" right="0.35433070866141736" top="0.39370078740157483" bottom="0.47244094488188981" header="0.51181102362204722" footer="0.23622047244094491"/>
   <pageSetup scale="57" firstPageNumber="0" fitToHeight="0" orientation="landscape" horizontalDpi="300" verticalDpi="300" ns3:id="rId3"/>
   <headerFooter alignWithMargins="0"/>
